--- a/artfynd/A 58743-2025 artfynd.xlsx
+++ b/artfynd/A 58743-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,58 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114045602</v>
+        <v>61712549</v>
       </c>
       <c r="B2" t="n">
-        <v>91591</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90674</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3100</v>
+        <v>1596</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Görjeån, Lu lm</t>
+          <t>Kilkokheden, Lu lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>752622</v>
+        <v>752715</v>
       </c>
       <c r="R2" t="n">
-        <v>7365952</v>
+        <v>7366114</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +750,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2016-09-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2016-09-30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,55 +764,51 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Lars Sundberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Rasmus Häggqvist</t>
+          <t>Lars Sundberg, Sonja Kuoljok</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114045591</v>
+        <v>114045602</v>
       </c>
       <c r="B3" t="n">
-        <v>91609</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4365</v>
+        <v>3100</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +818,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>752753</v>
+        <v>752622</v>
       </c>
       <c r="R3" t="n">
-        <v>7366015</v>
+        <v>7365952</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,37 +880,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114045607</v>
+        <v>114045633</v>
       </c>
       <c r="B4" t="n">
-        <v>91586</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6055</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>752698</v>
+        <v>752768</v>
       </c>
       <c r="R4" t="n">
-        <v>7365945</v>
+        <v>7366051</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,37 +977,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114045626</v>
+        <v>114045662</v>
       </c>
       <c r="B5" t="n">
-        <v>91609</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4365</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1012,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>752777</v>
+        <v>752784</v>
       </c>
       <c r="R5" t="n">
-        <v>7366035</v>
+        <v>7366033</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,15 +1074,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>114045621</v>
+        <v>114045618</v>
       </c>
       <c r="B6" t="n">
-        <v>91599</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1123,10 +1109,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>752647</v>
+        <v>752777</v>
       </c>
       <c r="R6" t="n">
-        <v>7365952</v>
+        <v>7366023</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,37 +1171,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>114045644</v>
+        <v>114045620</v>
       </c>
       <c r="B7" t="n">
-        <v>91609</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4365</v>
+        <v>4362</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1206,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>752619</v>
+        <v>752765</v>
       </c>
       <c r="R7" t="n">
-        <v>7365951</v>
+        <v>7366052</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,15 +1268,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>114045633</v>
+        <v>114045621</v>
       </c>
       <c r="B8" t="n">
-        <v>91597</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1303,21 +1279,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1303,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>752768</v>
+        <v>752647</v>
       </c>
       <c r="R8" t="n">
-        <v>7366051</v>
+        <v>7365952</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,15 +1365,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>114045618</v>
+        <v>114045627</v>
       </c>
       <c r="B9" t="n">
-        <v>91599</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1429,10 +1400,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>752777</v>
+        <v>752702</v>
       </c>
       <c r="R9" t="n">
-        <v>7366023</v>
+        <v>7365969</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,37 +1462,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>114045629</v>
+        <v>114045695</v>
       </c>
       <c r="B10" t="n">
-        <v>91609</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4365</v>
+        <v>4362</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1497,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>752694</v>
+        <v>752591</v>
       </c>
       <c r="R10" t="n">
-        <v>7365957</v>
+        <v>7366061</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1561,12 +1527,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1586,22 +1552,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Rasmus Häggqvist</t>
+          <t>Nils Bodin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>114045595</v>
+        <v>114045580</v>
       </c>
       <c r="B11" t="n">
-        <v>89025</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1609,21 +1570,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6276</v>
+        <v>4365</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1594,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>752745</v>
+        <v>752760</v>
       </c>
       <c r="R11" t="n">
-        <v>7366002</v>
+        <v>7366064</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,15 +1656,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>114045580</v>
+        <v>114045591</v>
       </c>
       <c r="B12" t="n">
-        <v>91609</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1735,10 +1691,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>752760</v>
+        <v>752753</v>
       </c>
       <c r="R12" t="n">
-        <v>7366064</v>
+        <v>7366015</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,37 +1753,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>114045620</v>
+        <v>114045623</v>
       </c>
       <c r="B13" t="n">
-        <v>91599</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4362</v>
+        <v>4365</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1788,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>752765</v>
+        <v>752760</v>
       </c>
       <c r="R13" t="n">
-        <v>7366052</v>
+        <v>7366088</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,37 +1850,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>114045614</v>
+        <v>114045626</v>
       </c>
       <c r="B14" t="n">
-        <v>8414</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>4365</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1885,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>752649</v>
+        <v>752777</v>
       </c>
       <c r="R14" t="n">
-        <v>7365956</v>
+        <v>7366035</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,37 +1947,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>114045601</v>
+        <v>114045629</v>
       </c>
       <c r="B15" t="n">
-        <v>8414</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>4365</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,7 +1982,7 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>752661</v>
+        <v>752694</v>
       </c>
       <c r="R15" t="n">
         <v>7365957</v>
@@ -2103,37 +2044,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>114045627</v>
+        <v>114045644</v>
       </c>
       <c r="B16" t="n">
-        <v>91599</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4362</v>
+        <v>4365</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2079,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>752702</v>
+        <v>752619</v>
       </c>
       <c r="R16" t="n">
-        <v>7365969</v>
+        <v>7365951</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,53 +2141,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>114045623</v>
+        <v>61712553</v>
       </c>
       <c r="B17" t="n">
-        <v>91609</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4365</v>
+        <v>4745</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Görjeån, Lu lm</t>
+          <t>Kilkokheden, Lu lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>752760</v>
+        <v>752715</v>
       </c>
       <c r="R17" t="n">
-        <v>7366088</v>
+        <v>7366114</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2275,12 +2208,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2016-09-30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2016-09-30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2289,33 +2222,29 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Lars Sundberg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Rasmus Häggqvist</t>
+          <t>Lars Sundberg, Sonja Kuoljok</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>114045662</v>
+        <v>114045714</v>
       </c>
       <c r="B18" t="n">
-        <v>91597</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2323,21 +2252,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4361</v>
+        <v>5448</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2276,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>752784</v>
+        <v>752599</v>
       </c>
       <c r="R18" t="n">
-        <v>7366033</v>
+        <v>7366048</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2377,12 +2306,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2402,44 +2331,39 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Rasmus Häggqvist</t>
+          <t>Nils Bodin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122575108</v>
+        <v>122575097</v>
       </c>
       <c r="B19" t="n">
-        <v>92262</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>232140</v>
+        <v>5448</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2452,10 +2376,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>752765</v>
+        <v>752773</v>
       </c>
       <c r="R19" t="n">
-        <v>7366072</v>
+        <v>7366027</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2515,15 +2439,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122575097</v>
+        <v>61712568</v>
       </c>
       <c r="B20" t="n">
-        <v>92259</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2531,40 +2450,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5448</v>
+        <v>5966</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Görjeån, Lu lm</t>
+          <t>Kilkokheden, Lu lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>752773</v>
+        <v>752715</v>
       </c>
       <c r="R20" t="n">
-        <v>7366027</v>
+        <v>7366114</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2588,12 +2506,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2016-09-30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2016-09-30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2609,15 +2527,601 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
+          <t>Lars Sundberg</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Lars Sundberg, Sonja Kuoljok</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>114045607</v>
+      </c>
+      <c r="B21" t="n">
+        <v>93181</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6055</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Spadskinn</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Stereopsis vitellina</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(S.Lundell) D.A.Reid</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Görjeån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>752698</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7365945</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
           <t>Rasmus Häggqvist</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>114045632</v>
+      </c>
+      <c r="B22" t="n">
+        <v>93181</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6055</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Spadskinn</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Stereopsis vitellina</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(S.Lundell) D.A.Reid</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Görjeån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>752601</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7365971</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
         <is>
           <t>Rasmus Häggqvist</t>
         </is>
       </c>
-      <c r="AY20" t="inlineStr"/>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>114045595</v>
+      </c>
+      <c r="B23" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Görjeån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>752745</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7366002</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Rasmus Häggqvist</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>114045601</v>
+      </c>
+      <c r="B24" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Görjeån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>752661</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7365957</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Rasmus Häggqvist</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>114045614</v>
+      </c>
+      <c r="B25" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Görjeån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>752649</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7365956</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Rasmus Häggqvist</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>122575108</v>
+      </c>
+      <c r="B26" t="n">
+        <v>93228</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Görjeån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>752765</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7366072</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Rasmus Häggqvist</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Rasmus Häggqvist</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
